--- a/Table/TableAsset/TB_MonsterDrop.xlsx
+++ b/Table/TableAsset/TB_MonsterDrop.xlsx
@@ -485,27 +485,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>drop_id</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>mon_id</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>exp_amount</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>gold_amount</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>screw_amount</t>
         </is>
@@ -522,13 +522,13 @@
           <t>MON_001</t>
         </is>
       </c>
-      <c r="C2" s="2" t="n">
+      <c r="C2" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E2" s="3" t="n">
+      <c r="D2" t="n">
+        <v>5</v>
+      </c>
+      <c r="E2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -543,13 +543,13 @@
           <t>MON_002</t>
         </is>
       </c>
-      <c r="C3" s="2" t="n">
+      <c r="C3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="E3" s="3" t="n">
+      <c r="D3" t="n">
+        <v>3</v>
+      </c>
+      <c r="E3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -564,13 +564,13 @@
           <t>MON_003</t>
         </is>
       </c>
-      <c r="C4" s="2" t="n">
+      <c r="C4" t="n">
         <v>6</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="D4" t="n">
         <v>10</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="E4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -585,13 +585,13 @@
           <t>MON_004</t>
         </is>
       </c>
-      <c r="C5" s="2" t="n">
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="D5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="E5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -606,13 +606,13 @@
           <t>MON_BOSS_001</t>
         </is>
       </c>
-      <c r="C6" s="2" t="n">
+      <c r="C6" t="n">
         <v>50</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="D6" t="n">
         <v>200</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="E6" t="n">
         <v>20</v>
       </c>
     </row>
@@ -627,13 +627,13 @@
           <t>MON_006</t>
         </is>
       </c>
-      <c r="C7" s="2" t="n">
+      <c r="C7" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E7" s="3" t="n">
+      <c r="D7" t="n">
+        <v>5</v>
+      </c>
+      <c r="E7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -648,13 +648,13 @@
           <t>MON_007</t>
         </is>
       </c>
-      <c r="C8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E8" s="3" t="n">
+      <c r="C8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D8" t="n">
+        <v>5</v>
+      </c>
+      <c r="E8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -669,13 +669,13 @@
           <t>MON_008</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="D9" s="3" t="n">
-        <v>5</v>
-      </c>
-      <c r="E9" s="3" t="n">
+      <c r="C9" t="n">
+        <v>3</v>
+      </c>
+      <c r="D9" t="n">
+        <v>5</v>
+      </c>
+      <c r="E9" t="n">
         <v>0</v>
       </c>
     </row>
@@ -690,13 +690,13 @@
           <t>MON_009</t>
         </is>
       </c>
-      <c r="C10" s="2" t="n">
+      <c r="C10" t="n">
         <v>8</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="D10" t="n">
         <v>8</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="E10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -711,13 +711,13 @@
           <t>MON_010</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D11" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E11" s="4" t="n">
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="n">
+        <v>5</v>
+      </c>
+      <c r="E11" t="n">
         <v>0</v>
       </c>
     </row>
@@ -732,13 +732,13 @@
           <t>MON_011</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E12" s="4" t="n">
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="n">
+        <v>5</v>
+      </c>
+      <c r="E12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -753,13 +753,13 @@
           <t>MON_012</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E13" s="4" t="n">
+      <c r="C13" t="n">
+        <v>3</v>
+      </c>
+      <c r="D13" t="n">
+        <v>5</v>
+      </c>
+      <c r="E13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -774,13 +774,13 @@
           <t>MON_013</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D14" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E14" s="4" t="n">
+      <c r="C14" t="n">
+        <v>3</v>
+      </c>
+      <c r="D14" t="n">
+        <v>5</v>
+      </c>
+      <c r="E14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -795,13 +795,13 @@
           <t>MON_014</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D15" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E15" s="4" t="n">
+      <c r="C15" t="n">
+        <v>3</v>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
+      </c>
+      <c r="E15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -816,13 +816,13 @@
           <t>MON_015</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D16" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E16" s="4" t="n">
+      <c r="C16" t="n">
+        <v>3</v>
+      </c>
+      <c r="D16" t="n">
+        <v>5</v>
+      </c>
+      <c r="E16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -837,13 +837,13 @@
           <t>MON_016</t>
         </is>
       </c>
-      <c r="C17" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D17" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="C17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D17" t="n">
+        <v>5</v>
+      </c>
+      <c r="E17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -858,13 +858,13 @@
           <t>MON_017</t>
         </is>
       </c>
-      <c r="C18" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D18" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E18" s="4" t="n">
+      <c r="C18" t="n">
+        <v>3</v>
+      </c>
+      <c r="D18" t="n">
+        <v>5</v>
+      </c>
+      <c r="E18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -879,13 +879,13 @@
           <t>MON_018</t>
         </is>
       </c>
-      <c r="C19" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E19" s="4" t="n">
+      <c r="C19" t="n">
+        <v>3</v>
+      </c>
+      <c r="D19" t="n">
+        <v>5</v>
+      </c>
+      <c r="E19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -900,13 +900,13 @@
           <t>MON_019</t>
         </is>
       </c>
-      <c r="C20" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D20" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E20" s="4" t="n">
+      <c r="C20" t="n">
+        <v>3</v>
+      </c>
+      <c r="D20" t="n">
+        <v>5</v>
+      </c>
+      <c r="E20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -921,13 +921,13 @@
           <t>MON_020</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D21" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E21" s="4" t="n">
+      <c r="C21" t="n">
+        <v>3</v>
+      </c>
+      <c r="D21" t="n">
+        <v>5</v>
+      </c>
+      <c r="E21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -942,13 +942,13 @@
           <t>MON_021</t>
         </is>
       </c>
-      <c r="C22" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D22" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E22" s="4" t="n">
+      <c r="C22" t="n">
+        <v>3</v>
+      </c>
+      <c r="D22" t="n">
+        <v>5</v>
+      </c>
+      <c r="E22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -963,13 +963,13 @@
           <t>MON_022</t>
         </is>
       </c>
-      <c r="C23" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D23" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E23" s="4" t="n">
+      <c r="C23" t="n">
+        <v>3</v>
+      </c>
+      <c r="D23" t="n">
+        <v>5</v>
+      </c>
+      <c r="E23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -984,13 +984,13 @@
           <t>MON_023</t>
         </is>
       </c>
-      <c r="C24" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D24" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E24" s="4" t="n">
+      <c r="C24" t="n">
+        <v>3</v>
+      </c>
+      <c r="D24" t="n">
+        <v>5</v>
+      </c>
+      <c r="E24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1005,13 +1005,13 @@
           <t>MON_024</t>
         </is>
       </c>
-      <c r="C25" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E25" s="4" t="n">
+      <c r="C25" t="n">
+        <v>3</v>
+      </c>
+      <c r="D25" t="n">
+        <v>5</v>
+      </c>
+      <c r="E25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1026,13 +1026,13 @@
           <t>MON_025</t>
         </is>
       </c>
-      <c r="C26" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D26" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E26" s="4" t="n">
+      <c r="C26" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" t="n">
+        <v>5</v>
+      </c>
+      <c r="E26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1047,13 +1047,13 @@
           <t>MON_026</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D27" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E27" s="4" t="n">
+      <c r="C27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D27" t="n">
+        <v>5</v>
+      </c>
+      <c r="E27" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1068,13 +1068,13 @@
           <t>MON_027</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n">
-        <v>3</v>
-      </c>
-      <c r="D28" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="E28" s="4" t="n">
+      <c r="C28" t="n">
+        <v>3</v>
+      </c>
+      <c r="D28" t="n">
+        <v>5</v>
+      </c>
+      <c r="E28" t="n">
         <v>0</v>
       </c>
     </row>

--- a/Table/TableAsset/TB_MonsterDrop.xlsx
+++ b/Table/TableAsset/TB_MonsterDrop.xlsx
@@ -475,7 +475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -510,6 +510,16 @@
           <t>screw_amount</t>
         </is>
       </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>fuel_drop_rate</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>turret_drop_rate</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -531,6 +541,12 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
+      <c r="F2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G2" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -552,6 +568,12 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
+      <c r="F3" t="n">
+        <v>5</v>
+      </c>
+      <c r="G3" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -573,6 +595,12 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
+      <c r="F4" t="n">
+        <v>5</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -594,6 +622,12 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
+      <c r="F5" t="n">
+        <v>5</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -615,6 +649,12 @@
       <c r="E6" t="n">
         <v>20</v>
       </c>
+      <c r="F6" t="n">
+        <v>100</v>
+      </c>
+      <c r="G6" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -636,6 +676,12 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
+      <c r="F7" t="n">
+        <v>5</v>
+      </c>
+      <c r="G7" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -657,6 +703,12 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
+      <c r="F8" t="n">
+        <v>5</v>
+      </c>
+      <c r="G8" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -678,6 +730,12 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+      <c r="G9" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -699,6 +757,12 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
+      <c r="F10" t="n">
+        <v>5</v>
+      </c>
+      <c r="G10" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -720,6 +784,12 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
+      <c r="F11" t="n">
+        <v>5</v>
+      </c>
+      <c r="G11" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -741,6 +811,12 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
+      <c r="F12" t="n">
+        <v>5</v>
+      </c>
+      <c r="G12" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -762,6 +838,12 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
+      <c r="F13" t="n">
+        <v>5</v>
+      </c>
+      <c r="G13" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -783,6 +865,12 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
+      <c r="F14" t="n">
+        <v>5</v>
+      </c>
+      <c r="G14" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -804,6 +892,12 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" t="n">
+        <v>5</v>
+      </c>
+      <c r="G15" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -825,6 +919,12 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
+      <c r="F16" t="n">
+        <v>5</v>
+      </c>
+      <c r="G16" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -846,6 +946,12 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
+      <c r="F17" t="n">
+        <v>5</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -867,6 +973,12 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
+      <c r="F18" t="n">
+        <v>5</v>
+      </c>
+      <c r="G18" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -888,6 +1000,12 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
+      <c r="F19" t="n">
+        <v>5</v>
+      </c>
+      <c r="G19" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -909,6 +1027,12 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
+      <c r="F20" t="n">
+        <v>5</v>
+      </c>
+      <c r="G20" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -930,6 +1054,12 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
+      <c r="F21" t="n">
+        <v>5</v>
+      </c>
+      <c r="G21" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -951,6 +1081,12 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
+      <c r="F22" t="n">
+        <v>5</v>
+      </c>
+      <c r="G22" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -972,6 +1108,12 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
+      <c r="F23" t="n">
+        <v>5</v>
+      </c>
+      <c r="G23" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -993,6 +1135,12 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
+      <c r="F24" t="n">
+        <v>5</v>
+      </c>
+      <c r="G24" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1014,6 +1162,12 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
+      <c r="F25" t="n">
+        <v>5</v>
+      </c>
+      <c r="G25" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1035,6 +1189,12 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
+      <c r="F26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G26" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1056,6 +1216,12 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
+      <c r="F27" t="n">
+        <v>5</v>
+      </c>
+      <c r="G27" t="n">
+        <v>3</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1075,6 +1241,93 @@
         <v>5</v>
       </c>
       <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>DROP_SLAVE_0</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>MON_BOSS_SLAVE_0</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>2</v>
+      </c>
+      <c r="D29" t="n">
+        <v>3</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>15</v>
+      </c>
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>DROP_SLAVE_1</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>MON_BOSS_SLAVE_1</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>4</v>
+      </c>
+      <c r="D30" t="n">
+        <v>5</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>15</v>
+      </c>
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>DROP_TRAFFIC</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>MON_TRAFFIC</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E31" t="n">
+        <v>2</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
         <v>0</v>
       </c>
     </row>
